--- a/artfynd/A 49502-2025 artfynd.xlsx
+++ b/artfynd/A 49502-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109911287</v>
+        <v>112605961</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654288.3646399479</v>
+        <v>654308</v>
       </c>
       <c r="R2" t="n">
-        <v>7126864.534270149</v>
+        <v>7126820</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109911282</v>
+        <v>112605960</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654474.6122267348</v>
+        <v>654268</v>
       </c>
       <c r="R3" t="n">
-        <v>7126422.302645065</v>
+        <v>7126740</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,19 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109911288</v>
+        <v>112605957</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654288.7345710429</v>
+        <v>654475</v>
       </c>
       <c r="R4" t="n">
-        <v>7126900.727066782</v>
+        <v>7126422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109911283</v>
+        <v>112605963</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654304.5589498354</v>
+        <v>654289</v>
       </c>
       <c r="R5" t="n">
-        <v>7126445.169507634</v>
+        <v>7126901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109911285</v>
+        <v>112605958</v>
       </c>
       <c r="B6" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654267.9482426373</v>
+        <v>654305</v>
       </c>
       <c r="R6" t="n">
-        <v>7126740.603720243</v>
+        <v>7126445</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109911286</v>
+        <v>112605962</v>
       </c>
       <c r="B7" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654307.6052832836</v>
+        <v>654288</v>
       </c>
       <c r="R7" t="n">
-        <v>7126820.170203434</v>
+        <v>7126865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2022-10-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 49502-2025 artfynd.xlsx
+++ b/artfynd/A 49502-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605961</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605960</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605963</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605958</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605962</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>